--- a/Stimulus_Configurations.xlsx
+++ b/Stimulus_Configurations.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Flanker Compatibility Task\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\研究所\碩二下\The Applications of Computer Hardware and Programming Languages in Behavioral Experiments and Big-Data Analyses\Midtern Report\Flanker Compatibility Task\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35518B30-2E13-4499-A342-C7BF66645316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E03CD56-6698-4BA2-AFF8-A7676CD77E78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-83" yWindow="0" windowWidth="12166" windowHeight="14362" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Setting" sheetId="2" r:id="rId1"/>
@@ -37,22 +37,13 @@
     <t>target_type</t>
   </si>
   <si>
-    <t>compatibility</t>
-  </si>
-  <si>
     <t>dist_pos_x</t>
   </si>
   <si>
     <t>square</t>
   </si>
   <si>
-    <t>comp</t>
-  </si>
-  <si>
     <t>a</t>
-  </si>
-  <si>
-    <t>incomp</t>
   </si>
   <si>
     <t>diamond</t>
@@ -63,6 +54,15 @@
   <si>
     <t>target_idx</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cong</t>
+  </si>
+  <si>
+    <t>incong</t>
+  </si>
+  <si>
+    <t>condition</t>
   </si>
 </sst>
 </file>
@@ -402,16 +402,16 @@
         <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
         <v>0</v>
       </c>
       <c r="F1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
@@ -419,16 +419,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D2">
         <v>-10</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -439,16 +439,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D3">
         <v>-10</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -459,16 +459,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D4">
         <v>-10</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4">
         <v>2</v>
@@ -479,16 +479,16 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D5">
         <v>-10</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F5">
         <v>3</v>
@@ -499,16 +499,16 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D6">
         <v>-10</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F6">
         <v>4</v>
@@ -519,16 +519,16 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D7">
         <v>-10</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -539,16 +539,16 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D8">
         <v>10</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -559,16 +559,16 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D9">
         <v>10</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -579,16 +579,16 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D10">
         <v>10</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F10">
         <v>2</v>
@@ -599,16 +599,16 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D11">
         <v>10</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F11">
         <v>3</v>
@@ -619,16 +619,16 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D12">
         <v>10</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F12">
         <v>4</v>
@@ -639,16 +639,16 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D13">
         <v>10</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -659,16 +659,16 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C14" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D14">
         <v>-10</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -679,16 +679,16 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D15">
         <v>-10</v>
       </c>
       <c r="E15" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -699,16 +699,16 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C16" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D16">
         <v>-10</v>
       </c>
       <c r="E16" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F16">
         <v>2</v>
@@ -719,16 +719,16 @@
         <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C17" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D17">
         <v>-10</v>
       </c>
       <c r="E17" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F17">
         <v>3</v>
@@ -739,16 +739,16 @@
         <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C18" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D18">
         <v>-10</v>
       </c>
       <c r="E18" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F18">
         <v>4</v>
@@ -759,16 +759,16 @@
         <v>1</v>
       </c>
       <c r="B19" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C19" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D19">
         <v>-10</v>
       </c>
       <c r="E19" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -779,16 +779,16 @@
         <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C20" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D20">
         <v>10</v>
       </c>
       <c r="E20" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -799,16 +799,16 @@
         <v>1</v>
       </c>
       <c r="B21" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C21" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D21">
         <v>10</v>
       </c>
       <c r="E21" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -819,16 +819,16 @@
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C22" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D22">
         <v>10</v>
       </c>
       <c r="E22" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F22">
         <v>2</v>
@@ -839,16 +839,16 @@
         <v>1</v>
       </c>
       <c r="B23" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C23" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D23">
         <v>10</v>
       </c>
       <c r="E23" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F23">
         <v>3</v>
@@ -859,16 +859,16 @@
         <v>1</v>
       </c>
       <c r="B24" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C24" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D24">
         <v>10</v>
       </c>
       <c r="E24" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F24">
         <v>4</v>
@@ -879,16 +879,16 @@
         <v>1</v>
       </c>
       <c r="B25" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C25" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D25">
         <v>10</v>
       </c>
       <c r="E25" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F25">
         <v>5</v>
@@ -899,16 +899,16 @@
         <v>1</v>
       </c>
       <c r="B26" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C26" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D26">
         <v>-10</v>
       </c>
       <c r="E26" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -919,16 +919,16 @@
         <v>1</v>
       </c>
       <c r="B27" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C27" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D27">
         <v>-10</v>
       </c>
       <c r="E27" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F27">
         <v>1</v>
@@ -939,16 +939,16 @@
         <v>1</v>
       </c>
       <c r="B28" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C28" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D28">
         <v>-10</v>
       </c>
       <c r="E28" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F28">
         <v>2</v>
@@ -959,16 +959,16 @@
         <v>1</v>
       </c>
       <c r="B29" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C29" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D29">
         <v>-10</v>
       </c>
       <c r="E29" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F29">
         <v>3</v>
@@ -979,16 +979,16 @@
         <v>1</v>
       </c>
       <c r="B30" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C30" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D30">
         <v>-10</v>
       </c>
       <c r="E30" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F30">
         <v>4</v>
@@ -999,16 +999,16 @@
         <v>1</v>
       </c>
       <c r="B31" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C31" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D31">
         <v>-10</v>
       </c>
       <c r="E31" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F31">
         <v>5</v>
@@ -1019,16 +1019,16 @@
         <v>1</v>
       </c>
       <c r="B32" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C32" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D32">
         <v>10</v>
       </c>
       <c r="E32" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -1039,16 +1039,16 @@
         <v>1</v>
       </c>
       <c r="B33" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C33" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D33">
         <v>10</v>
       </c>
       <c r="E33" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F33">
         <v>1</v>
@@ -1059,16 +1059,16 @@
         <v>1</v>
       </c>
       <c r="B34" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C34" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D34">
         <v>10</v>
       </c>
       <c r="E34" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F34">
         <v>2</v>
@@ -1079,16 +1079,16 @@
         <v>1</v>
       </c>
       <c r="B35" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C35" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D35">
         <v>10</v>
       </c>
       <c r="E35" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F35">
         <v>3</v>
@@ -1099,16 +1099,16 @@
         <v>1</v>
       </c>
       <c r="B36" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C36" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D36">
         <v>10</v>
       </c>
       <c r="E36" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F36">
         <v>4</v>
@@ -1119,16 +1119,16 @@
         <v>1</v>
       </c>
       <c r="B37" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C37" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D37">
         <v>10</v>
       </c>
       <c r="E37" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F37">
         <v>5</v>
@@ -1139,16 +1139,16 @@
         <v>1</v>
       </c>
       <c r="B38" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C38" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D38">
         <v>-10</v>
       </c>
       <c r="E38" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -1159,16 +1159,16 @@
         <v>1</v>
       </c>
       <c r="B39" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C39" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D39">
         <v>-10</v>
       </c>
       <c r="E39" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F39">
         <v>1</v>
@@ -1179,16 +1179,16 @@
         <v>1</v>
       </c>
       <c r="B40" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C40" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D40">
         <v>-10</v>
       </c>
       <c r="E40" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F40">
         <v>2</v>
@@ -1199,16 +1199,16 @@
         <v>1</v>
       </c>
       <c r="B41" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C41" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D41">
         <v>-10</v>
       </c>
       <c r="E41" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F41">
         <v>3</v>
@@ -1219,16 +1219,16 @@
         <v>1</v>
       </c>
       <c r="B42" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C42" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D42">
         <v>-10</v>
       </c>
       <c r="E42" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F42">
         <v>4</v>
@@ -1239,16 +1239,16 @@
         <v>1</v>
       </c>
       <c r="B43" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C43" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D43">
         <v>-10</v>
       </c>
       <c r="E43" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F43">
         <v>5</v>
@@ -1259,16 +1259,16 @@
         <v>1</v>
       </c>
       <c r="B44" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C44" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D44">
         <v>10</v>
       </c>
       <c r="E44" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -1279,16 +1279,16 @@
         <v>1</v>
       </c>
       <c r="B45" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C45" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D45">
         <v>10</v>
       </c>
       <c r="E45" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F45">
         <v>1</v>
@@ -1299,16 +1299,16 @@
         <v>1</v>
       </c>
       <c r="B46" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C46" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D46">
         <v>10</v>
       </c>
       <c r="E46" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F46">
         <v>2</v>
@@ -1319,16 +1319,16 @@
         <v>1</v>
       </c>
       <c r="B47" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C47" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D47">
         <v>10</v>
       </c>
       <c r="E47" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F47">
         <v>3</v>
@@ -1339,16 +1339,16 @@
         <v>1</v>
       </c>
       <c r="B48" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C48" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D48">
         <v>10</v>
       </c>
       <c r="E48" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F48">
         <v>4</v>
@@ -1359,16 +1359,16 @@
         <v>1</v>
       </c>
       <c r="B49" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C49" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D49">
         <v>10</v>
       </c>
       <c r="E49" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F49">
         <v>5</v>
@@ -1379,16 +1379,16 @@
         <v>2</v>
       </c>
       <c r="B50" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C50" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D50">
         <v>-10</v>
       </c>
       <c r="E50" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F50">
         <v>0</v>
@@ -1399,16 +1399,16 @@
         <v>2</v>
       </c>
       <c r="B51" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C51" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D51">
         <v>-10</v>
       </c>
       <c r="E51" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F51">
         <v>1</v>
@@ -1419,16 +1419,16 @@
         <v>2</v>
       </c>
       <c r="B52" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C52" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D52">
         <v>-10</v>
       </c>
       <c r="E52" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F52">
         <v>2</v>
@@ -1439,16 +1439,16 @@
         <v>2</v>
       </c>
       <c r="B53" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C53" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D53">
         <v>-10</v>
       </c>
       <c r="E53" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F53">
         <v>3</v>
@@ -1459,16 +1459,16 @@
         <v>2</v>
       </c>
       <c r="B54" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C54" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D54">
         <v>-10</v>
       </c>
       <c r="E54" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F54">
         <v>4</v>
@@ -1479,16 +1479,16 @@
         <v>2</v>
       </c>
       <c r="B55" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C55" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D55">
         <v>-10</v>
       </c>
       <c r="E55" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F55">
         <v>5</v>
@@ -1499,16 +1499,16 @@
         <v>2</v>
       </c>
       <c r="B56" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C56" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D56">
         <v>10</v>
       </c>
       <c r="E56" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -1519,16 +1519,16 @@
         <v>2</v>
       </c>
       <c r="B57" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C57" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D57">
         <v>10</v>
       </c>
       <c r="E57" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F57">
         <v>1</v>
@@ -1539,16 +1539,16 @@
         <v>2</v>
       </c>
       <c r="B58" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C58" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D58">
         <v>10</v>
       </c>
       <c r="E58" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F58">
         <v>2</v>
@@ -1559,16 +1559,16 @@
         <v>2</v>
       </c>
       <c r="B59" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C59" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D59">
         <v>10</v>
       </c>
       <c r="E59" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F59">
         <v>3</v>
@@ -1579,16 +1579,16 @@
         <v>2</v>
       </c>
       <c r="B60" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C60" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D60">
         <v>10</v>
       </c>
       <c r="E60" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F60">
         <v>4</v>
@@ -1599,16 +1599,16 @@
         <v>2</v>
       </c>
       <c r="B61" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C61" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D61">
         <v>10</v>
       </c>
       <c r="E61" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F61">
         <v>5</v>
@@ -1619,16 +1619,16 @@
         <v>2</v>
       </c>
       <c r="B62" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C62" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D62">
         <v>-10</v>
       </c>
       <c r="E62" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -1639,16 +1639,16 @@
         <v>2</v>
       </c>
       <c r="B63" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C63" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D63">
         <v>-10</v>
       </c>
       <c r="E63" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F63">
         <v>1</v>
@@ -1659,16 +1659,16 @@
         <v>2</v>
       </c>
       <c r="B64" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C64" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D64">
         <v>-10</v>
       </c>
       <c r="E64" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F64">
         <v>2</v>
@@ -1679,16 +1679,16 @@
         <v>2</v>
       </c>
       <c r="B65" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C65" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D65">
         <v>-10</v>
       </c>
       <c r="E65" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F65">
         <v>3</v>
@@ -1699,16 +1699,16 @@
         <v>2</v>
       </c>
       <c r="B66" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C66" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D66">
         <v>-10</v>
       </c>
       <c r="E66" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F66">
         <v>4</v>
@@ -1719,16 +1719,16 @@
         <v>2</v>
       </c>
       <c r="B67" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C67" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D67">
         <v>-10</v>
       </c>
       <c r="E67" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F67">
         <v>5</v>
@@ -1739,16 +1739,16 @@
         <v>2</v>
       </c>
       <c r="B68" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C68" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D68">
         <v>10</v>
       </c>
       <c r="E68" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -1759,16 +1759,16 @@
         <v>2</v>
       </c>
       <c r="B69" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C69" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D69">
         <v>10</v>
       </c>
       <c r="E69" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F69">
         <v>1</v>
@@ -1779,16 +1779,16 @@
         <v>2</v>
       </c>
       <c r="B70" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C70" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D70">
         <v>10</v>
       </c>
       <c r="E70" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F70">
         <v>2</v>
@@ -1799,16 +1799,16 @@
         <v>2</v>
       </c>
       <c r="B71" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C71" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D71">
         <v>10</v>
       </c>
       <c r="E71" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F71">
         <v>3</v>
@@ -1819,16 +1819,16 @@
         <v>2</v>
       </c>
       <c r="B72" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C72" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D72">
         <v>10</v>
       </c>
       <c r="E72" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F72">
         <v>4</v>
@@ -1839,16 +1839,16 @@
         <v>2</v>
       </c>
       <c r="B73" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C73" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D73">
         <v>10</v>
       </c>
       <c r="E73" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F73">
         <v>5</v>
@@ -1859,16 +1859,16 @@
         <v>2</v>
       </c>
       <c r="B74" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C74" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D74">
         <v>-10</v>
       </c>
       <c r="E74" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -1879,16 +1879,16 @@
         <v>2</v>
       </c>
       <c r="B75" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C75" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D75">
         <v>-10</v>
       </c>
       <c r="E75" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F75">
         <v>1</v>
@@ -1899,16 +1899,16 @@
         <v>2</v>
       </c>
       <c r="B76" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C76" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D76">
         <v>-10</v>
       </c>
       <c r="E76" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F76">
         <v>2</v>
@@ -1919,16 +1919,16 @@
         <v>2</v>
       </c>
       <c r="B77" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C77" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D77">
         <v>-10</v>
       </c>
       <c r="E77" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F77">
         <v>3</v>
@@ -1939,16 +1939,16 @@
         <v>2</v>
       </c>
       <c r="B78" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C78" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D78">
         <v>-10</v>
       </c>
       <c r="E78" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F78">
         <v>4</v>
@@ -1959,16 +1959,16 @@
         <v>2</v>
       </c>
       <c r="B79" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C79" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D79">
         <v>-10</v>
       </c>
       <c r="E79" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F79">
         <v>5</v>
@@ -1979,16 +1979,16 @@
         <v>2</v>
       </c>
       <c r="B80" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C80" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D80">
         <v>10</v>
       </c>
       <c r="E80" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F80">
         <v>0</v>
@@ -1999,16 +1999,16 @@
         <v>2</v>
       </c>
       <c r="B81" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C81" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D81">
         <v>10</v>
       </c>
       <c r="E81" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F81">
         <v>1</v>
@@ -2019,16 +2019,16 @@
         <v>2</v>
       </c>
       <c r="B82" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C82" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D82">
         <v>10</v>
       </c>
       <c r="E82" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F82">
         <v>2</v>
@@ -2039,16 +2039,16 @@
         <v>2</v>
       </c>
       <c r="B83" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C83" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D83">
         <v>10</v>
       </c>
       <c r="E83" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F83">
         <v>3</v>
@@ -2059,16 +2059,16 @@
         <v>2</v>
       </c>
       <c r="B84" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C84" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D84">
         <v>10</v>
       </c>
       <c r="E84" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F84">
         <v>4</v>
@@ -2079,16 +2079,16 @@
         <v>2</v>
       </c>
       <c r="B85" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C85" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D85">
         <v>10</v>
       </c>
       <c r="E85" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F85">
         <v>5</v>
@@ -2099,16 +2099,16 @@
         <v>2</v>
       </c>
       <c r="B86" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C86" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D86">
         <v>-10</v>
       </c>
       <c r="E86" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -2119,16 +2119,16 @@
         <v>2</v>
       </c>
       <c r="B87" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C87" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D87">
         <v>-10</v>
       </c>
       <c r="E87" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F87">
         <v>1</v>
@@ -2139,16 +2139,16 @@
         <v>2</v>
       </c>
       <c r="B88" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C88" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D88">
         <v>-10</v>
       </c>
       <c r="E88" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F88">
         <v>2</v>
@@ -2159,16 +2159,16 @@
         <v>2</v>
       </c>
       <c r="B89" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C89" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D89">
         <v>-10</v>
       </c>
       <c r="E89" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F89">
         <v>3</v>
@@ -2179,16 +2179,16 @@
         <v>2</v>
       </c>
       <c r="B90" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C90" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D90">
         <v>-10</v>
       </c>
       <c r="E90" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F90">
         <v>4</v>
@@ -2199,16 +2199,16 @@
         <v>2</v>
       </c>
       <c r="B91" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C91" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D91">
         <v>-10</v>
       </c>
       <c r="E91" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F91">
         <v>5</v>
@@ -2219,16 +2219,16 @@
         <v>2</v>
       </c>
       <c r="B92" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C92" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D92">
         <v>10</v>
       </c>
       <c r="E92" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F92">
         <v>0</v>
@@ -2239,16 +2239,16 @@
         <v>2</v>
       </c>
       <c r="B93" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C93" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D93">
         <v>10</v>
       </c>
       <c r="E93" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F93">
         <v>1</v>
@@ -2259,16 +2259,16 @@
         <v>2</v>
       </c>
       <c r="B94" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C94" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D94">
         <v>10</v>
       </c>
       <c r="E94" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F94">
         <v>2</v>
@@ -2279,16 +2279,16 @@
         <v>2</v>
       </c>
       <c r="B95" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C95" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D95">
         <v>10</v>
       </c>
       <c r="E95" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F95">
         <v>3</v>
@@ -2299,16 +2299,16 @@
         <v>2</v>
       </c>
       <c r="B96" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C96" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D96">
         <v>10</v>
       </c>
       <c r="E96" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F96">
         <v>4</v>
@@ -2319,16 +2319,16 @@
         <v>2</v>
       </c>
       <c r="B97" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C97" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D97">
         <v>10</v>
       </c>
       <c r="E97" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F97">
         <v>5</v>
@@ -2339,16 +2339,16 @@
         <v>3</v>
       </c>
       <c r="B98" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C98" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D98">
         <v>-10</v>
       </c>
       <c r="E98" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F98">
         <v>0</v>
@@ -2359,16 +2359,16 @@
         <v>3</v>
       </c>
       <c r="B99" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C99" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D99">
         <v>-10</v>
       </c>
       <c r="E99" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F99">
         <v>1</v>
@@ -2379,16 +2379,16 @@
         <v>3</v>
       </c>
       <c r="B100" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C100" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D100">
         <v>-10</v>
       </c>
       <c r="E100" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F100">
         <v>2</v>
@@ -2399,16 +2399,16 @@
         <v>3</v>
       </c>
       <c r="B101" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C101" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D101">
         <v>-10</v>
       </c>
       <c r="E101" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F101">
         <v>3</v>
@@ -2419,16 +2419,16 @@
         <v>3</v>
       </c>
       <c r="B102" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C102" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D102">
         <v>-10</v>
       </c>
       <c r="E102" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F102">
         <v>4</v>
@@ -2439,16 +2439,16 @@
         <v>3</v>
       </c>
       <c r="B103" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C103" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D103">
         <v>-10</v>
       </c>
       <c r="E103" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F103">
         <v>5</v>
@@ -2459,16 +2459,16 @@
         <v>3</v>
       </c>
       <c r="B104" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C104" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D104">
         <v>10</v>
       </c>
       <c r="E104" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F104">
         <v>0</v>
@@ -2479,16 +2479,16 @@
         <v>3</v>
       </c>
       <c r="B105" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C105" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D105">
         <v>10</v>
       </c>
       <c r="E105" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F105">
         <v>1</v>
@@ -2499,16 +2499,16 @@
         <v>3</v>
       </c>
       <c r="B106" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C106" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D106">
         <v>10</v>
       </c>
       <c r="E106" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F106">
         <v>2</v>
@@ -2519,16 +2519,16 @@
         <v>3</v>
       </c>
       <c r="B107" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C107" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D107">
         <v>10</v>
       </c>
       <c r="E107" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F107">
         <v>3</v>
@@ -2539,16 +2539,16 @@
         <v>3</v>
       </c>
       <c r="B108" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C108" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D108">
         <v>10</v>
       </c>
       <c r="E108" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F108">
         <v>4</v>
@@ -2559,16 +2559,16 @@
         <v>3</v>
       </c>
       <c r="B109" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C109" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D109">
         <v>10</v>
       </c>
       <c r="E109" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F109">
         <v>5</v>
@@ -2579,16 +2579,16 @@
         <v>3</v>
       </c>
       <c r="B110" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C110" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D110">
         <v>-10</v>
       </c>
       <c r="E110" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F110">
         <v>0</v>
@@ -2599,16 +2599,16 @@
         <v>3</v>
       </c>
       <c r="B111" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C111" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D111">
         <v>-10</v>
       </c>
       <c r="E111" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F111">
         <v>1</v>
@@ -2619,16 +2619,16 @@
         <v>3</v>
       </c>
       <c r="B112" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C112" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D112">
         <v>-10</v>
       </c>
       <c r="E112" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F112">
         <v>2</v>
@@ -2639,16 +2639,16 @@
         <v>3</v>
       </c>
       <c r="B113" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C113" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D113">
         <v>-10</v>
       </c>
       <c r="E113" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F113">
         <v>3</v>
@@ -2659,16 +2659,16 @@
         <v>3</v>
       </c>
       <c r="B114" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C114" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D114">
         <v>-10</v>
       </c>
       <c r="E114" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F114">
         <v>4</v>
@@ -2679,16 +2679,16 @@
         <v>3</v>
       </c>
       <c r="B115" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C115" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D115">
         <v>-10</v>
       </c>
       <c r="E115" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F115">
         <v>5</v>
@@ -2699,16 +2699,16 @@
         <v>3</v>
       </c>
       <c r="B116" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C116" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D116">
         <v>10</v>
       </c>
       <c r="E116" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F116">
         <v>0</v>
@@ -2719,16 +2719,16 @@
         <v>3</v>
       </c>
       <c r="B117" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C117" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D117">
         <v>10</v>
       </c>
       <c r="E117" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F117">
         <v>1</v>
@@ -2739,16 +2739,16 @@
         <v>3</v>
       </c>
       <c r="B118" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C118" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D118">
         <v>10</v>
       </c>
       <c r="E118" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F118">
         <v>2</v>
@@ -2759,16 +2759,16 @@
         <v>3</v>
       </c>
       <c r="B119" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C119" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D119">
         <v>10</v>
       </c>
       <c r="E119" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F119">
         <v>3</v>
@@ -2779,16 +2779,16 @@
         <v>3</v>
       </c>
       <c r="B120" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C120" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D120">
         <v>10</v>
       </c>
       <c r="E120" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F120">
         <v>4</v>
@@ -2799,16 +2799,16 @@
         <v>3</v>
       </c>
       <c r="B121" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C121" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D121">
         <v>10</v>
       </c>
       <c r="E121" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F121">
         <v>5</v>
@@ -2819,16 +2819,16 @@
         <v>3</v>
       </c>
       <c r="B122" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C122" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D122">
         <v>-10</v>
       </c>
       <c r="E122" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F122">
         <v>0</v>
@@ -2839,16 +2839,16 @@
         <v>3</v>
       </c>
       <c r="B123" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C123" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D123">
         <v>-10</v>
       </c>
       <c r="E123" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F123">
         <v>1</v>
@@ -2859,16 +2859,16 @@
         <v>3</v>
       </c>
       <c r="B124" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C124" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D124">
         <v>-10</v>
       </c>
       <c r="E124" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F124">
         <v>2</v>
@@ -2879,16 +2879,16 @@
         <v>3</v>
       </c>
       <c r="B125" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C125" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D125">
         <v>-10</v>
       </c>
       <c r="E125" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F125">
         <v>3</v>
@@ -2899,16 +2899,16 @@
         <v>3</v>
       </c>
       <c r="B126" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C126" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D126">
         <v>-10</v>
       </c>
       <c r="E126" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F126">
         <v>4</v>
@@ -2919,16 +2919,16 @@
         <v>3</v>
       </c>
       <c r="B127" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C127" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D127">
         <v>-10</v>
       </c>
       <c r="E127" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F127">
         <v>5</v>
@@ -2939,16 +2939,16 @@
         <v>3</v>
       </c>
       <c r="B128" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C128" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D128">
         <v>10</v>
       </c>
       <c r="E128" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F128">
         <v>0</v>
@@ -2959,16 +2959,16 @@
         <v>3</v>
       </c>
       <c r="B129" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C129" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D129">
         <v>10</v>
       </c>
       <c r="E129" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F129">
         <v>1</v>
@@ -2979,16 +2979,16 @@
         <v>3</v>
       </c>
       <c r="B130" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C130" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D130">
         <v>10</v>
       </c>
       <c r="E130" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F130">
         <v>2</v>
@@ -2999,16 +2999,16 @@
         <v>3</v>
       </c>
       <c r="B131" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C131" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D131">
         <v>10</v>
       </c>
       <c r="E131" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F131">
         <v>3</v>
@@ -3019,16 +3019,16 @@
         <v>3</v>
       </c>
       <c r="B132" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C132" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D132">
         <v>10</v>
       </c>
       <c r="E132" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F132">
         <v>4</v>
@@ -3039,16 +3039,16 @@
         <v>3</v>
       </c>
       <c r="B133" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C133" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D133">
         <v>10</v>
       </c>
       <c r="E133" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F133">
         <v>5</v>
@@ -3059,16 +3059,16 @@
         <v>3</v>
       </c>
       <c r="B134" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C134" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D134">
         <v>-10</v>
       </c>
       <c r="E134" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F134">
         <v>0</v>
@@ -3079,16 +3079,16 @@
         <v>3</v>
       </c>
       <c r="B135" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C135" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D135">
         <v>-10</v>
       </c>
       <c r="E135" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F135">
         <v>1</v>
@@ -3099,16 +3099,16 @@
         <v>3</v>
       </c>
       <c r="B136" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C136" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D136">
         <v>-10</v>
       </c>
       <c r="E136" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F136">
         <v>2</v>
@@ -3119,16 +3119,16 @@
         <v>3</v>
       </c>
       <c r="B137" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C137" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D137">
         <v>-10</v>
       </c>
       <c r="E137" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F137">
         <v>3</v>
@@ -3139,16 +3139,16 @@
         <v>3</v>
       </c>
       <c r="B138" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C138" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D138">
         <v>-10</v>
       </c>
       <c r="E138" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F138">
         <v>4</v>
@@ -3159,16 +3159,16 @@
         <v>3</v>
       </c>
       <c r="B139" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C139" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D139">
         <v>-10</v>
       </c>
       <c r="E139" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F139">
         <v>5</v>
@@ -3179,16 +3179,16 @@
         <v>3</v>
       </c>
       <c r="B140" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C140" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D140">
         <v>10</v>
       </c>
       <c r="E140" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F140">
         <v>0</v>
@@ -3199,16 +3199,16 @@
         <v>3</v>
       </c>
       <c r="B141" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C141" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D141">
         <v>10</v>
       </c>
       <c r="E141" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F141">
         <v>1</v>
@@ -3219,16 +3219,16 @@
         <v>3</v>
       </c>
       <c r="B142" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C142" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D142">
         <v>10</v>
       </c>
       <c r="E142" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F142">
         <v>2</v>
@@ -3239,16 +3239,16 @@
         <v>3</v>
       </c>
       <c r="B143" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C143" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D143">
         <v>10</v>
       </c>
       <c r="E143" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F143">
         <v>3</v>
@@ -3259,16 +3259,16 @@
         <v>3</v>
       </c>
       <c r="B144" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C144" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D144">
         <v>10</v>
       </c>
       <c r="E144" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F144">
         <v>4</v>
@@ -3279,16 +3279,16 @@
         <v>3</v>
       </c>
       <c r="B145" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C145" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D145">
         <v>10</v>
       </c>
       <c r="E145" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F145">
         <v>5</v>
@@ -3299,16 +3299,16 @@
         <v>4</v>
       </c>
       <c r="B146" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C146" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D146">
         <v>-10</v>
       </c>
       <c r="E146" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F146">
         <v>0</v>
@@ -3319,16 +3319,16 @@
         <v>4</v>
       </c>
       <c r="B147" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C147" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D147">
         <v>-10</v>
       </c>
       <c r="E147" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F147">
         <v>1</v>
@@ -3339,16 +3339,16 @@
         <v>4</v>
       </c>
       <c r="B148" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C148" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D148">
         <v>-10</v>
       </c>
       <c r="E148" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F148">
         <v>2</v>
@@ -3359,16 +3359,16 @@
         <v>4</v>
       </c>
       <c r="B149" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C149" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D149">
         <v>-10</v>
       </c>
       <c r="E149" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F149">
         <v>3</v>
@@ -3379,16 +3379,16 @@
         <v>4</v>
       </c>
       <c r="B150" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C150" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D150">
         <v>-10</v>
       </c>
       <c r="E150" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F150">
         <v>4</v>
@@ -3399,16 +3399,16 @@
         <v>4</v>
       </c>
       <c r="B151" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C151" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D151">
         <v>-10</v>
       </c>
       <c r="E151" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F151">
         <v>5</v>
@@ -3419,16 +3419,16 @@
         <v>4</v>
       </c>
       <c r="B152" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C152" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D152">
         <v>10</v>
       </c>
       <c r="E152" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F152">
         <v>0</v>
@@ -3439,16 +3439,16 @@
         <v>4</v>
       </c>
       <c r="B153" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C153" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D153">
         <v>10</v>
       </c>
       <c r="E153" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F153">
         <v>1</v>
@@ -3459,16 +3459,16 @@
         <v>4</v>
       </c>
       <c r="B154" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C154" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D154">
         <v>10</v>
       </c>
       <c r="E154" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F154">
         <v>2</v>
@@ -3479,16 +3479,16 @@
         <v>4</v>
       </c>
       <c r="B155" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C155" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D155">
         <v>10</v>
       </c>
       <c r="E155" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F155">
         <v>3</v>
@@ -3499,16 +3499,16 @@
         <v>4</v>
       </c>
       <c r="B156" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C156" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D156">
         <v>10</v>
       </c>
       <c r="E156" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F156">
         <v>4</v>
@@ -3519,16 +3519,16 @@
         <v>4</v>
       </c>
       <c r="B157" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C157" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D157">
         <v>10</v>
       </c>
       <c r="E157" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F157">
         <v>5</v>
@@ -3539,16 +3539,16 @@
         <v>4</v>
       </c>
       <c r="B158" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C158" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D158">
         <v>-10</v>
       </c>
       <c r="E158" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F158">
         <v>0</v>
@@ -3559,16 +3559,16 @@
         <v>4</v>
       </c>
       <c r="B159" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C159" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D159">
         <v>-10</v>
       </c>
       <c r="E159" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F159">
         <v>1</v>
@@ -3579,16 +3579,16 @@
         <v>4</v>
       </c>
       <c r="B160" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C160" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D160">
         <v>-10</v>
       </c>
       <c r="E160" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F160">
         <v>2</v>
@@ -3599,16 +3599,16 @@
         <v>4</v>
       </c>
       <c r="B161" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C161" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D161">
         <v>-10</v>
       </c>
       <c r="E161" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F161">
         <v>3</v>
@@ -3619,16 +3619,16 @@
         <v>4</v>
       </c>
       <c r="B162" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C162" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D162">
         <v>-10</v>
       </c>
       <c r="E162" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F162">
         <v>4</v>
@@ -3639,16 +3639,16 @@
         <v>4</v>
       </c>
       <c r="B163" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C163" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D163">
         <v>-10</v>
       </c>
       <c r="E163" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F163">
         <v>5</v>
@@ -3659,16 +3659,16 @@
         <v>4</v>
       </c>
       <c r="B164" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C164" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D164">
         <v>10</v>
       </c>
       <c r="E164" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F164">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>4</v>
       </c>
       <c r="B165" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C165" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D165">
         <v>10</v>
       </c>
       <c r="E165" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F165">
         <v>1</v>
@@ -3699,16 +3699,16 @@
         <v>4</v>
       </c>
       <c r="B166" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C166" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D166">
         <v>10</v>
       </c>
       <c r="E166" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F166">
         <v>2</v>
@@ -3719,16 +3719,16 @@
         <v>4</v>
       </c>
       <c r="B167" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C167" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D167">
         <v>10</v>
       </c>
       <c r="E167" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F167">
         <v>3</v>
@@ -3739,16 +3739,16 @@
         <v>4</v>
       </c>
       <c r="B168" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C168" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D168">
         <v>10</v>
       </c>
       <c r="E168" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F168">
         <v>4</v>
@@ -3759,16 +3759,16 @@
         <v>4</v>
       </c>
       <c r="B169" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C169" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D169">
         <v>10</v>
       </c>
       <c r="E169" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F169">
         <v>5</v>
@@ -3779,16 +3779,16 @@
         <v>4</v>
       </c>
       <c r="B170" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C170" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D170">
         <v>-10</v>
       </c>
       <c r="E170" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F170">
         <v>0</v>
@@ -3799,16 +3799,16 @@
         <v>4</v>
       </c>
       <c r="B171" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C171" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D171">
         <v>-10</v>
       </c>
       <c r="E171" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F171">
         <v>1</v>
@@ -3819,16 +3819,16 @@
         <v>4</v>
       </c>
       <c r="B172" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C172" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D172">
         <v>-10</v>
       </c>
       <c r="E172" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F172">
         <v>2</v>
@@ -3839,16 +3839,16 @@
         <v>4</v>
       </c>
       <c r="B173" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C173" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D173">
         <v>-10</v>
       </c>
       <c r="E173" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F173">
         <v>3</v>
@@ -3859,16 +3859,16 @@
         <v>4</v>
       </c>
       <c r="B174" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C174" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D174">
         <v>-10</v>
       </c>
       <c r="E174" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F174">
         <v>4</v>
@@ -3879,16 +3879,16 @@
         <v>4</v>
       </c>
       <c r="B175" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C175" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D175">
         <v>-10</v>
       </c>
       <c r="E175" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F175">
         <v>5</v>
@@ -3899,16 +3899,16 @@
         <v>4</v>
       </c>
       <c r="B176" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C176" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D176">
         <v>10</v>
       </c>
       <c r="E176" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F176">
         <v>0</v>
@@ -3919,16 +3919,16 @@
         <v>4</v>
       </c>
       <c r="B177" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C177" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D177">
         <v>10</v>
       </c>
       <c r="E177" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F177">
         <v>1</v>
@@ -3939,16 +3939,16 @@
         <v>4</v>
       </c>
       <c r="B178" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C178" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D178">
         <v>10</v>
       </c>
       <c r="E178" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F178">
         <v>2</v>
@@ -3959,16 +3959,16 @@
         <v>4</v>
       </c>
       <c r="B179" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C179" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D179">
         <v>10</v>
       </c>
       <c r="E179" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F179">
         <v>3</v>
@@ -3979,16 +3979,16 @@
         <v>4</v>
       </c>
       <c r="B180" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C180" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D180">
         <v>10</v>
       </c>
       <c r="E180" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F180">
         <v>4</v>
@@ -3999,16 +3999,16 @@
         <v>4</v>
       </c>
       <c r="B181" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C181" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D181">
         <v>10</v>
       </c>
       <c r="E181" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F181">
         <v>5</v>
@@ -4019,16 +4019,16 @@
         <v>4</v>
       </c>
       <c r="B182" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C182" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D182">
         <v>-10</v>
       </c>
       <c r="E182" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F182">
         <v>0</v>
@@ -4039,16 +4039,16 @@
         <v>4</v>
       </c>
       <c r="B183" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C183" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D183">
         <v>-10</v>
       </c>
       <c r="E183" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F183">
         <v>1</v>
@@ -4059,16 +4059,16 @@
         <v>4</v>
       </c>
       <c r="B184" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C184" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D184">
         <v>-10</v>
       </c>
       <c r="E184" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F184">
         <v>2</v>
@@ -4079,16 +4079,16 @@
         <v>4</v>
       </c>
       <c r="B185" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C185" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D185">
         <v>-10</v>
       </c>
       <c r="E185" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F185">
         <v>3</v>
@@ -4099,16 +4099,16 @@
         <v>4</v>
       </c>
       <c r="B186" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C186" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D186">
         <v>-10</v>
       </c>
       <c r="E186" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F186">
         <v>4</v>
@@ -4119,16 +4119,16 @@
         <v>4</v>
       </c>
       <c r="B187" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C187" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D187">
         <v>-10</v>
       </c>
       <c r="E187" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F187">
         <v>5</v>
@@ -4139,16 +4139,16 @@
         <v>4</v>
       </c>
       <c r="B188" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C188" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D188">
         <v>10</v>
       </c>
       <c r="E188" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F188">
         <v>0</v>
@@ -4159,16 +4159,16 @@
         <v>4</v>
       </c>
       <c r="B189" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C189" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D189">
         <v>10</v>
       </c>
       <c r="E189" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F189">
         <v>1</v>
@@ -4179,16 +4179,16 @@
         <v>4</v>
       </c>
       <c r="B190" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C190" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D190">
         <v>10</v>
       </c>
       <c r="E190" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F190">
         <v>2</v>
@@ -4199,16 +4199,16 @@
         <v>4</v>
       </c>
       <c r="B191" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C191" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D191">
         <v>10</v>
       </c>
       <c r="E191" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F191">
         <v>3</v>
@@ -4219,16 +4219,16 @@
         <v>4</v>
       </c>
       <c r="B192" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C192" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D192">
         <v>10</v>
       </c>
       <c r="E192" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F192">
         <v>4</v>
@@ -4239,16 +4239,16 @@
         <v>4</v>
       </c>
       <c r="B193" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C193" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D193">
         <v>10</v>
       </c>
       <c r="E193" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F193">
         <v>5</v>
